--- a/artfynd/A 18647-2024 artfynd.xlsx
+++ b/artfynd/A 18647-2024 artfynd.xlsx
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117579710</v>
+        <v>117579616</v>
       </c>
       <c r="B10" t="n">
-        <v>90513</v>
+        <v>78217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481971</v>
+        <v>481826</v>
       </c>
       <c r="R10" t="n">
-        <v>6918767</v>
+        <v>6918644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117579638</v>
+        <v>117579710</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>90513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,25 +1724,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481914</v>
+        <v>481971</v>
       </c>
       <c r="R11" t="n">
-        <v>6918672</v>
+        <v>6918767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117579604</v>
+        <v>117579633</v>
       </c>
       <c r="B12" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>481662</v>
+        <v>481867</v>
       </c>
       <c r="R12" t="n">
-        <v>6918518</v>
+        <v>6918701</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117579560</v>
+        <v>117579472</v>
       </c>
       <c r="B13" t="n">
-        <v>56499</v>
+        <v>78216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,35 +1936,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1972,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481705</v>
+        <v>481832</v>
       </c>
       <c r="R13" t="n">
-        <v>6918516</v>
+        <v>6918451</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,6 +2011,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2034,10 +2030,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117579637</v>
+        <v>117579497</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2042,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2077,10 +2073,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>481861</v>
+        <v>481832</v>
       </c>
       <c r="R14" t="n">
-        <v>6918709</v>
+        <v>6918451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117579614</v>
+        <v>117579768</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>78125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2152,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481678</v>
+        <v>481927</v>
       </c>
       <c r="R15" t="n">
-        <v>6918519</v>
+        <v>6918666</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2246,10 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117579633</v>
+        <v>117579629</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2262,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2289,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481867</v>
+        <v>481945</v>
       </c>
       <c r="R16" t="n">
-        <v>6918701</v>
+        <v>6918731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117579629</v>
+        <v>117579638</v>
       </c>
       <c r="B17" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2364,25 +2360,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481945</v>
+        <v>481914</v>
       </c>
       <c r="R17" t="n">
-        <v>6918731</v>
+        <v>6918672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2458,10 +2454,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117579497</v>
+        <v>117579637</v>
       </c>
       <c r="B18" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2470,25 +2466,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2501,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481832</v>
+        <v>481861</v>
       </c>
       <c r="R18" t="n">
-        <v>6918451</v>
+        <v>6918709</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,10 +2560,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117579616</v>
+        <v>117579614</v>
       </c>
       <c r="B19" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,25 +2572,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2607,10 +2603,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481826</v>
+        <v>481678</v>
       </c>
       <c r="R19" t="n">
-        <v>6918644</v>
+        <v>6918519</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117579472</v>
+        <v>117579560</v>
       </c>
       <c r="B20" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2682,30 +2678,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2713,10 +2714,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481832</v>
+        <v>481705</v>
       </c>
       <c r="R20" t="n">
-        <v>6918451</v>
+        <v>6918516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2757,7 +2758,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2776,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117579768</v>
+        <v>117579604</v>
       </c>
       <c r="B21" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2792,21 +2792,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481927</v>
+        <v>481662</v>
       </c>
       <c r="R21" t="n">
-        <v>6918666</v>
+        <v>6918518</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 18647-2024 artfynd.xlsx
+++ b/artfynd/A 18647-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117579518</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>117579529</v>
       </c>
       <c r="B3" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117579616</v>
+        <v>117579472</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,21 +1622,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>481826</v>
+        <v>481832</v>
       </c>
       <c r="R10" t="n">
-        <v>6918644</v>
+        <v>6918451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117579710</v>
+        <v>117579629</v>
       </c>
       <c r="B11" t="n">
-        <v>90513</v>
+        <v>78219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,21 +1728,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>481971</v>
+        <v>481945</v>
       </c>
       <c r="R11" t="n">
-        <v>6918767</v>
+        <v>6918731</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1821,7 +1821,7 @@
         <v>117579633</v>
       </c>
       <c r="B12" t="n">
-        <v>78216</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,17 +1917,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117579472</v>
+        <v>117579614</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,25 +1936,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>481832</v>
+        <v>481678</v>
       </c>
       <c r="R13" t="n">
-        <v>6918451</v>
+        <v>6918519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         <v>117579497</v>
       </c>
       <c r="B14" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117579768</v>
+        <v>117579638</v>
       </c>
       <c r="B15" t="n">
-        <v>78125</v>
+        <v>91774</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>481927</v>
+        <v>481914</v>
       </c>
       <c r="R15" t="n">
-        <v>6918666</v>
+        <v>6918672</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2235,17 +2235,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117579629</v>
+        <v>117579768</v>
       </c>
       <c r="B16" t="n">
-        <v>78217</v>
+        <v>78127</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2258,21 +2258,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>481945</v>
+        <v>481927</v>
       </c>
       <c r="R16" t="n">
-        <v>6918731</v>
+        <v>6918666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,10 +2348,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117579638</v>
+        <v>117579616</v>
       </c>
       <c r="B17" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2360,25 +2360,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>481914</v>
+        <v>481826</v>
       </c>
       <c r="R17" t="n">
-        <v>6918672</v>
+        <v>6918644</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,17 +2447,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117579637</v>
+        <v>117579604</v>
       </c>
       <c r="B18" t="n">
-        <v>91772</v>
+        <v>79100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2466,25 +2466,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>481861</v>
+        <v>481662</v>
       </c>
       <c r="R18" t="n">
-        <v>6918709</v>
+        <v>6918518</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117579614</v>
+        <v>117579560</v>
       </c>
       <c r="B19" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2576,26 +2576,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2603,10 +2608,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>481678</v>
+        <v>481705</v>
       </c>
       <c r="R19" t="n">
-        <v>6918519</v>
+        <v>6918516</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,7 +2652,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2666,10 +2670,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117579560</v>
+        <v>117579710</v>
       </c>
       <c r="B20" t="n">
-        <v>56499</v>
+        <v>90515</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2678,35 +2682,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2714,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>481705</v>
+        <v>481971</v>
       </c>
       <c r="R20" t="n">
-        <v>6918516</v>
+        <v>6918767</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2758,6 +2757,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2776,10 +2776,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117579604</v>
+        <v>117579637</v>
       </c>
       <c r="B21" t="n">
-        <v>79098</v>
+        <v>91774</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2788,25 +2788,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>481662</v>
+        <v>481861</v>
       </c>
       <c r="R21" t="n">
-        <v>6918518</v>
+        <v>6918709</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Sebastian Kirppu</t>
+          <t>Sebastian Kirppu, Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
